--- a/artfynd/A 27393-2026 artfynd.xlsx
+++ b/artfynd/A 27393-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119298297</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -780,12 +775,7 @@
         <v>119298294</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119298296</v>
+        <v>119298299</v>
       </c>
       <c r="B4" t="n">
-        <v>79643</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583411</v>
+        <v>583220</v>
       </c>
       <c r="R4" t="n">
-        <v>6978407</v>
+        <v>6978594</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119298299</v>
+        <v>119298298</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583220</v>
+        <v>583236</v>
       </c>
       <c r="R5" t="n">
-        <v>6978594</v>
+        <v>6978523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119298295</v>
+        <v>119298296</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583431</v>
+        <v>583411</v>
       </c>
       <c r="R6" t="n">
-        <v>6978402</v>
+        <v>6978407</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119298298</v>
+        <v>119298295</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583236</v>
+        <v>583431</v>
       </c>
       <c r="R7" t="n">
-        <v>6978523</v>
+        <v>6978402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 27393-2026 artfynd.xlsx
+++ b/artfynd/A 27393-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119298297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119298299</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119298298</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119298294</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119298296</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119298295</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>